--- a/docs/google-sheets-template/Letter_Dispatcher_Contacts_Template.xlsx
+++ b/docs/google-sheets-template/Letter_Dispatcher_Contacts_Template.xlsx
@@ -110,42 +110,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCE8FA"/>
+        <fgColor rgb="00D9E1EE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E0F2E5"/>
+        <fgColor rgb="00DAE7DF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EAE0F7"/>
+        <fgColor rgb="00E7DFF1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FBF0CB"/>
+        <fgColor rgb="00EDE9D7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9F2EE"/>
+        <fgColor rgb="00D7E7E6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FBE2EA"/>
+        <fgColor rgb="00EEDCE6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE8D5"/>
+        <fgColor rgb="00F1E4D8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E7E9E6"/>
+        <fgColor rgb="00E2E4E3"/>
       </patternFill>
     </fill>
     <fill>
@@ -244,56 +244,64 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00DCE8FA"/>
+          <fgColor rgb="00D9E1EE"/>
+          <bgColor rgb="00D9E1EE"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00E0F2E5"/>
+          <fgColor rgb="00DAE7DF"/>
+          <bgColor rgb="00DAE7DF"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00EAE0F7"/>
+          <fgColor rgb="00E7DFF1"/>
+          <bgColor rgb="00E7DFF1"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FBF0CB"/>
+          <fgColor rgb="00EDE9D7"/>
+          <bgColor rgb="00EDE9D7"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00D9F2EE"/>
+          <fgColor rgb="00D7E7E6"/>
+          <bgColor rgb="00D7E7E6"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FBE2EA"/>
+          <fgColor rgb="00EEDCE6"/>
+          <bgColor rgb="00EEDCE6"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FCE8D5"/>
+          <fgColor rgb="00F1E4D8"/>
+          <bgColor rgb="00F1E4D8"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00E7E9E6"/>
+          <fgColor rgb="00E2E4E3"/>
+          <bgColor rgb="00E2E4E3"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1962,7 +1970,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="D2:D200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Custom group" error="Choose a group from the list, or type your own — this is just a suggestion, not a strict rule." type="list">
-      <formula1>=GroupNamesList</formula1>
+      <formula1>GroupNamesList</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1989,10 +1997,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="82" customHeight="1">
+    <row r="2" ht="96" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>These are the choices offered in the Group dropdown on the Contacts sheet, and the color each matching row gets tinted there. Rename any value below or replace it with your own — the dropdown and the row colors update immediately, everywhere in this file.</t>
+          <t>These are the choices offered in the Group dropdown on the Contacts sheet, and the color each matching row gets tinted there. Rename any value below or replace it with your own — the dropdown and the row colors update immediately, everywhere in this file (in Excel — this sheet isn't a live source when the file is opened in Google Sheets).</t>
         </is>
       </c>
     </row>
@@ -2227,14 +2235,15 @@
     <row r="29" ht="22" customHeight="1">
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>5. Customize the group names</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="74" customHeight="1">
+          <t>5. Customize the group names (in Excel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="100" customHeight="1">
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>Open the “Group Names” sheet (tab at the bottom of this file) to rename any of the eight options, or replace them with your own — the dropdown on the Contacts sheet and the row colors above update immediately, everywhere in this file.
+          <t>Open the “Group Names” sheet (tab at the bottom of this file) to rename any of the eight options, or replace them with your own — in Excel, the dropdown on the Contacts sheet and the row colors above update immediately, everywhere in this file.
+In Google Sheets this link unfortunately doesn't work (a Google Sheets limitation — it doesn't support conditional-format formulas that reference another sheet), so there the colors and dropdown stay as they are.
 Contacts that already have the old name keep it as plain text; use Find &amp; Replace (Ctrl+H / ⌘+H) on the Group column if you want to update them too.</t>
         </is>
       </c>
@@ -2415,14 +2424,15 @@
     <row r="29" ht="22" customHeight="1">
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>5. Personnaliser les noms de groupes</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="74" customHeight="1">
+          <t>5. Personnaliser les noms de groupes (dans Excel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="100" customHeight="1">
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>Ouvrez la feuille « Group Names » (onglet en bas de ce fichier) pour renommer l'une des huit options, ou la remplacer par la vôtre — la liste déroulante de la feuille Contacts et les couleurs de lignes ci-dessus se mettent à jour immédiatement, partout dans ce fichier.
+          <t>Ouvrez la feuille « Group Names » (onglet en bas de ce fichier) pour renommer l'une des huit options, ou la remplacer par la vôtre — dans Excel, la liste déroulante de la feuille Contacts et les couleurs de lignes ci-dessus se mettent à jour immédiatement, partout dans ce fichier.
+Dans Google Sheets, ce lien ne fonctionne malheureusement pas (une limitation de Google Sheets — il ne prend pas en charge les formules de mise en forme conditionnelle faisant référence à une autre feuille), donc là-bas les couleurs et la liste déroulante restent inchangées.
 Les contacts qui ont déjà l'ancien nom le gardent en texte simple ; utilisez Rechercher/Remplacer (Ctrl+H / ⌘+H) sur la colonne Group si vous voulez aussi les mettre à jour.</t>
         </is>
       </c>
@@ -2603,14 +2613,15 @@
     <row r="29" ht="22" customHeight="1">
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>5. Настройка названий групп</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="74" customHeight="1">
+          <t>5. Настройка названий групп (в Excel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="100" customHeight="1">
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>Откройте лист «Group Names» (вкладка внизу этого файла), чтобы переименовать любой из восьми вариантов или заменить его своим — выпадающий список на листе Contacts и цвета строк выше обновятся сразу же, во всём файле.
+          <t>Откройте лист «Group Names» (вкладка внизу этого файла), чтобы переименовать любой из восьми вариантов или заменить его своим — в Excel выпадающий список на листе Contacts и цвета строк выше обновятся сразу же, во всём файле.
+В Google Sheets эта связь, к сожалению, не работает (ограничение самого Google Sheets — оно не поддерживает формулы условного форматирования, ссылающиеся на другой лист), поэтому там подсветка и выпадающий список останутся как есть.
 Контакты, у которых уже стоит старое название, сохранят его как обычный текст — если нужно обновить и их, используйте Найти и заменить (Ctrl+H) по столбцу Group.</t>
         </is>
       </c>
